--- a/survey_templates/043_training_needs_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/043_training_needs_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'high school'}</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'some college'}</t>
+          <t>some college</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'university'}</t>
+          <t>university</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'graduate_degree'}</t>
+          <t>graduate_degree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'graduate degree'}</t>
+          <t>graduate degree</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'male'}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'female'}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'problem-solving'}</t>
+          <t>problem-solving</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'problem-solving'}</t>
+          <t>problem-solving</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'english'}</t>
+          <t>english</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'french'}</t>
+          <t>french</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'english'}</t>
+          <t>english</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'french'}</t>
+          <t>french</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
     </row>
